--- a/漢字（かんじ）/b.xlsx
+++ b/漢字（かんじ）/b.xlsx
@@ -89,7 +89,10 @@
   </si>
   <si>
     <t>一番｜いちばん
-番号｜ばんごう</t>
+番号｜ばんごう
+順番｜じゅんばん
+当番｜とうばん
+当番表｜とうばんひょう</t>
   </si>
   <si>
     <t>判</t>
@@ -393,7 +396,9 @@
   <si>
     <t>防水｜ぼうすい
 防止｜ぼうし
-防犯｜ぼうはん</t>
+防犯｜ぼうはん
+防災｜ぼうさい
+防災訓練｜ぼうさいくんれん</t>
   </si>
   <si>
     <t>美貌｜びぼう</t>
@@ -453,7 +458,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -485,13 +490,6 @@
       <color rgb="FFFF0000"/>
       <name val="等线"/>
       <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -955,148 +953,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1504,7 +1502,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" ht="34.2" customHeight="1" spans="1:7">
+    <row r="5" ht="69" spans="1:7">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
@@ -1966,7 +1964,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="4" ht="54" spans="1:3">
+    <row r="4" ht="90" spans="1:3">
       <c r="A4" s="1" t="s">
         <v>87</v>
       </c>

--- a/漢字（かんじ）/b.xlsx
+++ b/漢字（かんじ）/b.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" activeTab="4"/>
+    <workbookView windowWidth="23040" windowHeight="9180" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="ば" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="108">
   <si>
     <t>仮名</t>
   </si>
@@ -65,7 +65,8 @@
   <si>
     <t>爆発｜ばくはつ
 爆笑｜ばくしょう
-爆笑的｜ばくしょうてき</t>
+爆笑的｜ばくしょうてき
+爆弾｜ばくだん</t>
   </si>
   <si>
     <t>ばん</t>
@@ -285,6 +286,12 @@
     <t>武術｜ぶじゅつ</t>
   </si>
   <si>
+    <t>無</t>
+  </si>
+  <si>
+    <t>無礼｜ぶれい</t>
+  </si>
+  <si>
     <t>ぶん</t>
   </si>
   <si>
@@ -422,6 +429,12 @@
   </si>
   <si>
     <t>貿易｜ぼうえき</t>
+  </si>
+  <si>
+    <t>冒</t>
+  </si>
+  <si>
+    <t>冒険｜ぼうけん</t>
   </si>
   <si>
     <t>望</t>
@@ -1732,8 +1745,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelRow="6" outlineLevelCol="6"/>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelRow="7" outlineLevelCol="6"/>
   <cols>
     <col min="3" max="3" width="23.6666666666667" customWidth="1"/>
     <col min="7" max="7" width="22.6666666666667" customWidth="1"/>
@@ -1812,26 +1825,37 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6" ht="54" spans="1:7">
+    <row r="6" ht="18" spans="1:7">
       <c r="A6" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C6" s="3" t="s">
+    </row>
+    <row r="7" ht="54" spans="1:7">
+      <c r="A7" s="1" t="s">
         <v>68</v>
-      </c>
-    </row>
-    <row r="7" ht="180" spans="1:7">
-      <c r="A7" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>70</v>
+      </c>
+    </row>
+    <row r="8" ht="180" spans="1:7">
+      <c r="A8" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1863,57 +1887,57 @@
     </row>
     <row r="2" ht="126" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" ht="36" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" ht="36" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>43</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" ht="36" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -1925,7 +1949,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="3" max="3" width="28.6666666666667" customWidth="1"/>
@@ -1944,112 +1968,123 @@
     </row>
     <row r="2" ht="31.8" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" ht="36" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" ht="90" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" ht="56.4" customHeight="1" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C7" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="9" ht="72" spans="1:3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="9" ht="18" spans="1:3">
       <c r="A9" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="10" ht="18" spans="1:3">
-      <c r="A10" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B10" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
+    <row r="10" ht="72" spans="1:3">
+      <c r="A10" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C10" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C11" t="s">
+    </row>
+    <row r="11" ht="18" spans="1:3">
+      <c r="A11" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>103</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>105</v>
+      </c>
+      <c r="B12" t="s">
+        <v>106</v>
+      </c>
+      <c r="C12" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/漢字（かんじ）/b.xlsx
+++ b/漢字（かんじ）/b.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" activeTab="2"/>
+    <workbookView windowWidth="22188" windowHeight="9180" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="ば" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="110">
   <si>
     <t>仮名</t>
   </si>
@@ -361,6 +361,12 @@
   </si>
   <si>
     <t>ぼ</t>
+  </si>
+  <si>
+    <t>母</t>
+  </si>
+  <si>
+    <t>母校｜ぼこう</t>
   </si>
   <si>
     <t>簿</t>
@@ -1949,7 +1955,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="3" max="3" width="28.6666666666667" customWidth="1"/>
@@ -1966,86 +1972,86 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" ht="31.8" spans="1:3">
+    <row r="2" ht="18" spans="1:3">
       <c r="A2" s="1" t="s">
         <v>84</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="3" ht="36" spans="1:3">
+    <row r="3" ht="31.8" spans="1:3">
       <c r="A3" s="1" t="s">
         <v>84</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="4" ht="90" spans="1:3">
+    <row r="4" ht="36" spans="1:3">
       <c r="A4" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C4" s="3" t="s">
+    </row>
+    <row r="5" ht="90" spans="1:3">
+      <c r="A5" s="1" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="5" ht="18" spans="1:3">
-      <c r="A5" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="6" ht="18" spans="1:3">
+      <c r="A6" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="6" ht="56.4" customHeight="1" spans="1:3">
-      <c r="A6" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="7" ht="18" spans="1:3">
+    <row r="7" ht="56.4" customHeight="1" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B7" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B7" t="s">
         <v>95</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="3" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:3">
       <c r="A9" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>99</v>
@@ -2054,37 +2060,48 @@
         <v>100</v>
       </c>
     </row>
-    <row r="10" ht="72" spans="1:3">
+    <row r="10" ht="18" spans="1:3">
       <c r="A10" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="1" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="11" ht="18" spans="1:3">
-      <c r="A11" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B11" s="4" t="s">
+    <row r="11" ht="72" spans="1:3">
+      <c r="A11" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="3" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
+    <row r="12" ht="18" spans="1:3">
+      <c r="A12" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C12" t="s">
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
         <v>107</v>
+      </c>
+      <c r="B13" t="s">
+        <v>108</v>
+      </c>
+      <c r="C13" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/漢字（かんじ）/b.xlsx
+++ b/漢字（かんじ）/b.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" activeTab="4"/>
+    <workbookView windowWidth="22188" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="ば" sheetId="1" r:id="rId1"/>
@@ -137,7 +137,8 @@
   <si>
     <t>抜群｜ばつぐん
 効果抜群｜こうかばつぐん
-抜擢｜ばってき</t>
+抜擢｜ばってき
+海抜｜かいばつ</t>
   </si>
   <si>
     <t>び</t>
@@ -1584,7 +1585,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" ht="54" spans="1:7">
+    <row r="11" ht="72" spans="1:7">
       <c r="A11" s="1" t="s">
         <v>26</v>
       </c>

--- a/漢字（かんじ）/b.xlsx
+++ b/漢字（かんじ）/b.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="111">
   <si>
     <t>仮名</t>
   </si>
@@ -117,10 +117,14 @@
   <si>
     <t>売店｜ばいてん
 自動販売機｜じどうはんばいき
-発売｜はつばい</t>
+発売｜はつばい
+好評発売中｜こうひょうはつばいちゅう</t>
   </si>
   <si>
     <t>杯</t>
+  </si>
+  <si>
+    <t>一杯｜いっぱい</t>
   </si>
   <si>
     <t>買</t>
@@ -1555,7 +1559,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" ht="54" spans="1:7">
+    <row r="8" ht="90" spans="1:7">
       <c r="A8" s="1" t="s">
         <v>18</v>
       </c>
@@ -1573,27 +1577,30 @@
       <c r="B9" s="1" t="s">
         <v>23</v>
       </c>
+      <c r="C9" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="10" ht="18" spans="1:7">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" ht="72" spans="1:7">
       <c r="A11" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1624,120 +1631,120 @@
     </row>
     <row r="2" ht="72" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" ht="54" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" ht="36" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" ht="37.8" customHeight="1" spans="1:3">
       <c r="A9" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:3">
       <c r="A10" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:3">
       <c r="A11" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" ht="49.8" spans="1:3">
       <c r="A12" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:3">
@@ -1781,88 +1788,88 @@
     </row>
     <row r="2" ht="70.2" customHeight="1" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:7">
       <c r="A4" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:7">
       <c r="A5" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:7">
       <c r="A6" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" ht="54" spans="1:7">
       <c r="A7" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" ht="180" spans="1:7">
       <c r="A8" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -1894,57 +1901,57 @@
     </row>
     <row r="2" ht="126" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" ht="36" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" ht="36" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" ht="36" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -1975,134 +1982,134 @@
     </row>
     <row r="2" ht="18" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" ht="31.8" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" ht="36" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" ht="90" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" ht="56.4" customHeight="1" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:3">
       <c r="A9" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:3">
       <c r="A10" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11" ht="72" spans="1:3">
       <c r="A11" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C13" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
